--- a/excels/faculty.xlsx
+++ b/excels/faculty.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27932"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\code\nitw\NITW-Transportation-Division\excels\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\NIT\Documents\PA_Catts\Nitw_WB\excels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61CF74B5-A67D-455B-B7E8-6F22FDFA9619}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D404DBB9-C461-44A0-89D3-74E03914ECA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CoreFaculty" sheetId="1" r:id="rId1"/>
@@ -24,12 +24,15 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="159">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="170">
   <si>
     <t>Name</t>
   </si>
@@ -298,9 +301,6 @@
     <t>https://erp.nitw.ac.in/ext/profile/ce-ss</t>
   </si>
   <si>
-    <t>Email</t>
-  </si>
-  <si>
     <t>Research Areas</t>
   </si>
   <si>
@@ -439,9 +439,6 @@
     <t>GoogleScholar</t>
   </si>
   <si>
-    <t>N/A</t>
-  </si>
-  <si>
     <t>https://orcid.org/0000-0002-1680-2089</t>
   </si>
   <si>
@@ -506,6 +503,46 @@
   </si>
   <si>
     <t>Characterization for asphalt binders and mixtures; asphalt pavement analysis, design and evaluation; quantification of roadway and railway traffic noise</t>
+  </si>
+  <si>
+    <t xml:space="preserve">University </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Association </t>
+  </si>
+  <si>
+    <t>Carmelo D'agostino</t>
+  </si>
+  <si>
+    <t>Senior lecturer</t>
+  </si>
+  <si>
+    <t>carmelo.dagostino@tft.lth.se</t>
+  </si>
+  <si>
+    <t>Aliaksei Laureshyn</t>
+  </si>
+  <si>
+    <t> aliaksei.laureshyn@tft.lth.se</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lund University </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spark </t>
+  </si>
+  <si>
+    <t>Traffic Safety , Road Safety, Pedestrian Safety, Surrogate measures of safety , Traffic Conflicts , Bicycle safety, 
+Video Analysis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Safety , Transportation, Traffic Engineering, Transportation Planning, Transport Engineering, Simulation, Transport Management, Risk Assessment, Sustainable Development </t>
+  </si>
+  <si>
+    <t>images/Guest Faculty/Aliaksei Laureshyn.jpg"</t>
+  </si>
+  <si>
+    <t>images/Guest Faculty/Carmelo D'agostino.jpg</t>
   </si>
 </sst>
 </file>
@@ -676,7 +713,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
@@ -714,6 +751,15 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1020,37 +1066,37 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>116</v>
+      </c>
+      <c r="C1" t="s">
+        <v>118</v>
+      </c>
+      <c r="D1" t="s">
+        <v>119</v>
+      </c>
+      <c r="E1" t="s">
+        <v>120</v>
+      </c>
+      <c r="F1" t="s">
+        <v>121</v>
+      </c>
+      <c r="G1" t="s">
         <v>117</v>
       </c>
-      <c r="C1" t="s">
-        <v>119</v>
-      </c>
-      <c r="D1" t="s">
-        <v>120</v>
-      </c>
-      <c r="E1" t="s">
-        <v>121</v>
-      </c>
-      <c r="F1" t="s">
+      <c r="H1" t="s">
         <v>122</v>
       </c>
-      <c r="G1" t="s">
-        <v>118</v>
-      </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>123</v>
       </c>
-      <c r="I1" t="s">
-        <v>124</v>
-      </c>
       <c r="J1" t="s">
+        <v>132</v>
+      </c>
+      <c r="K1" t="s">
         <v>133</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>134</v>
-      </c>
-      <c r="L1" t="s">
-        <v>135</v>
       </c>
       <c r="M1" t="s">
         <v>1</v>
@@ -1085,19 +1131,19 @@
         <v>2</v>
       </c>
       <c r="H2" s="13" t="s">
+        <v>124</v>
+      </c>
+      <c r="I2" s="14" t="s">
         <v>125</v>
       </c>
-      <c r="I2" s="14" t="s">
-        <v>126</v>
-      </c>
       <c r="J2" s="15" t="s">
+        <v>135</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="L2" s="2" t="s">
         <v>137</v>
-      </c>
-      <c r="K2" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="L2" s="2" t="s">
-        <v>139</v>
       </c>
       <c r="M2" t="s">
         <v>31</v>
@@ -1135,19 +1181,19 @@
         <v>1</v>
       </c>
       <c r="H3" s="13" t="s">
+        <v>126</v>
+      </c>
+      <c r="I3" s="13" t="s">
         <v>127</v>
       </c>
-      <c r="I3" s="13" t="s">
-        <v>128</v>
-      </c>
       <c r="J3" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="L3" s="2" t="s">
         <v>140</v>
-      </c>
-      <c r="K3" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="L3" s="2" t="s">
-        <v>142</v>
       </c>
       <c r="M3" t="s">
         <v>31</v>
@@ -1182,19 +1228,19 @@
         <v>8</v>
       </c>
       <c r="H4" s="13" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="I4" s="13" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="J4" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="K4" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="L4" t="s">
         <v>143</v>
-      </c>
-      <c r="K4" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="L4" t="s">
-        <v>145</v>
       </c>
       <c r="M4" t="s">
         <v>6</v>
@@ -1232,19 +1278,19 @@
         <v>1</v>
       </c>
       <c r="H5" s="14" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="I5" s="14" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="J5" t="s">
+        <v>144</v>
+      </c>
+      <c r="K5" t="s">
+        <v>145</v>
+      </c>
+      <c r="L5" t="s">
         <v>146</v>
-      </c>
-      <c r="K5" t="s">
-        <v>147</v>
-      </c>
-      <c r="L5" t="s">
-        <v>148</v>
       </c>
       <c r="M5" t="s">
         <v>80</v>
@@ -1282,19 +1328,19 @@
         <v>3</v>
       </c>
       <c r="H6" s="13" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="I6" s="13" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="J6" t="s">
+        <v>147</v>
+      </c>
+      <c r="K6" t="s">
+        <v>148</v>
+      </c>
+      <c r="L6" t="s">
         <v>149</v>
-      </c>
-      <c r="K6" t="s">
-        <v>150</v>
-      </c>
-      <c r="L6" t="s">
-        <v>151</v>
       </c>
       <c r="M6" t="s">
         <v>80</v>
@@ -1329,19 +1375,19 @@
         <v>7</v>
       </c>
       <c r="H7" s="13" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="I7" s="13" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="J7" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="L7" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="M7" t="s">
         <v>80</v>
@@ -1353,7 +1399,7 @@
         <v>81</v>
       </c>
       <c r="P7" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="Q7" s="2" t="s">
         <v>82</v>
@@ -1376,19 +1422,19 @@
         <v>9</v>
       </c>
       <c r="H8" s="14" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="I8" s="14" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="J8" t="s">
+        <v>151</v>
+      </c>
+      <c r="K8" t="s">
+        <v>152</v>
+      </c>
+      <c r="L8" t="s">
         <v>153</v>
-      </c>
-      <c r="K8" t="s">
-        <v>154</v>
-      </c>
-      <c r="L8" t="s">
-        <v>155</v>
       </c>
       <c r="M8" t="s">
         <v>12</v>
@@ -1527,134 +1573,162 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.140625" customWidth="1"/>
-    <col min="2" max="2" width="14" customWidth="1"/>
-    <col min="3" max="3" width="18.42578125" customWidth="1"/>
-    <col min="4" max="4" width="37.85546875" customWidth="1"/>
-    <col min="5" max="5" width="29.42578125" customWidth="1"/>
-    <col min="6" max="6" width="22.7109375" customWidth="1"/>
+    <col min="2" max="4" width="24.5703125" customWidth="1"/>
+    <col min="5" max="5" width="37.85546875" customWidth="1"/>
+    <col min="6" max="6" width="29.42578125" customWidth="1"/>
+    <col min="7" max="7" width="22.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
-        <v>2</v>
+      <c r="C1" s="16" t="s">
+        <v>157</v>
       </c>
       <c r="D1" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="E1" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="F1" s="3" t="s">
+      <c r="G1" s="3" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="4" t="s">
-        <v>136</v>
-      </c>
-      <c r="B2" s="4"/>
-      <c r="C2" s="4"/>
-      <c r="D2" s="4"/>
-      <c r="E2" s="4"/>
-      <c r="F2" s="4"/>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="4" t="s">
-        <v>136</v>
-      </c>
-      <c r="B3" s="4"/>
-      <c r="C3" s="4"/>
-      <c r="D3" s="4"/>
-      <c r="E3" s="4"/>
-      <c r="F3" s="4"/>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="4" t="s">
-        <v>136</v>
-      </c>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>162</v>
+      </c>
+      <c r="B2" t="s">
+        <v>160</v>
+      </c>
+      <c r="C2" s="18" t="s">
+        <v>164</v>
+      </c>
+      <c r="D2" s="17" t="s">
+        <v>165</v>
+      </c>
+      <c r="E2" t="s">
+        <v>163</v>
+      </c>
+      <c r="F2" t="s">
+        <v>166</v>
+      </c>
+      <c r="G2" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>159</v>
+      </c>
+      <c r="B3" t="s">
+        <v>160</v>
+      </c>
+      <c r="C3" s="17" t="s">
+        <v>164</v>
+      </c>
+      <c r="D3" s="17" t="s">
+        <v>165</v>
+      </c>
+      <c r="E3" t="s">
+        <v>161</v>
+      </c>
+      <c r="F3" t="s">
+        <v>167</v>
+      </c>
+      <c r="G3" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" s="4"/>
       <c r="B4" s="4"/>
       <c r="C4" s="4"/>
       <c r="D4" s="4"/>
       <c r="E4" s="4"/>
       <c r="F4" s="4"/>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="4" t="s">
-        <v>136</v>
-      </c>
+      <c r="G4" s="4"/>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" s="4"/>
       <c r="B5" s="4"/>
       <c r="C5" s="4"/>
       <c r="D5" s="4"/>
       <c r="E5" s="4"/>
       <c r="F5" s="4"/>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="4" t="s">
-        <v>136</v>
-      </c>
+      <c r="G5" s="4"/>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" s="4"/>
       <c r="B6" s="4"/>
       <c r="C6" s="4"/>
       <c r="D6" s="4"/>
       <c r="E6" s="4"/>
       <c r="F6" s="4"/>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="4" t="s">
-        <v>136</v>
-      </c>
+      <c r="G6" s="4"/>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" s="4"/>
       <c r="B7" s="4"/>
       <c r="C7" s="4"/>
       <c r="D7" s="4"/>
       <c r="E7" s="4"/>
       <c r="F7" s="4"/>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="4" t="s">
-        <v>136</v>
-      </c>
+      <c r="G7" s="4"/>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" s="4"/>
       <c r="B8" s="4"/>
       <c r="C8" s="4"/>
       <c r="D8" s="4"/>
       <c r="E8" s="4"/>
       <c r="F8" s="4"/>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="4" t="s">
-        <v>136</v>
-      </c>
+      <c r="G8" s="4"/>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" s="4"/>
       <c r="B9" s="4"/>
       <c r="C9" s="4"/>
       <c r="D9" s="4"/>
       <c r="E9" s="4"/>
       <c r="F9" s="4"/>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G9" s="4"/>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="4"/>
       <c r="B10" s="4"/>
       <c r="C10" s="4"/>
       <c r="D10" s="4"/>
       <c r="E10" s="4"/>
       <c r="F10" s="4"/>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G10" s="4"/>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="4"/>
       <c r="B11" s="4"/>
       <c r="C11" s="4"/>
       <c r="D11" s="4"/>
       <c r="E11" s="4"/>
       <c r="F11" s="4"/>
+      <c r="G11" s="4"/>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="E3" r:id="rId1" display="https://portal.research.lu.se/en/persons/carmelo-dagostino/" xr:uid="{BB1D5C0B-7EE0-405C-981B-7A52C90A3CA8}"/>
+    <hyperlink ref="E2" r:id="rId2" display="mailto:aliaksei.laureshyn@tft.lth.se" xr:uid="{427A828D-746B-478A-9530-7EDB1E3A7067}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -1682,7 +1756,7 @@
         <v>48</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
@@ -1690,7 +1764,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C2">
         <v>1969</v>
@@ -1744,7 +1818,7 @@
         <v>1997</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
@@ -1776,7 +1850,7 @@
         <v>1971</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
@@ -1853,7 +1927,7 @@
         <v>2007</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
@@ -1915,7 +1989,7 @@
         <v>2007</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
@@ -1947,7 +2021,7 @@
         <v>2000</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
@@ -1964,7 +2038,7 @@
         <v>1993</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
@@ -1981,7 +2055,7 @@
         <v>1993</v>
       </c>
       <c r="E20" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
@@ -1998,7 +2072,7 @@
         <v>2003</v>
       </c>
       <c r="E21" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
@@ -2015,7 +2089,7 @@
         <v>2004</v>
       </c>
       <c r="E22" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
@@ -2032,7 +2106,7 @@
         <v>2003</v>
       </c>
       <c r="E23" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
@@ -2049,7 +2123,7 @@
         <v>2004</v>
       </c>
       <c r="E24" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
@@ -2110,7 +2184,7 @@
         <v>2013</v>
       </c>
       <c r="E28" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
@@ -2142,7 +2216,7 @@
         <v>2017</v>
       </c>
       <c r="E30" s="4" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
@@ -2167,7 +2241,7 @@
   <sheetData>
     <row r="1" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="5" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B1" s="6" t="s">
         <v>0</v>
@@ -2187,7 +2261,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C2" s="9">
         <v>1968</v>
@@ -2202,7 +2276,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C3" s="9">
         <v>1970</v>
@@ -2217,7 +2291,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C4" s="9">
         <v>1978</v>
@@ -2226,7 +2300,7 @@
         <v>1987</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -2234,7 +2308,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C5" s="9">
         <v>1987</v>
@@ -2243,7 +2317,7 @@
         <v>1990</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -2251,7 +2325,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C6" s="9">
         <v>1990</v>
@@ -2260,7 +2334,7 @@
         <v>1993</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -2268,7 +2342,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C7" s="9">
         <v>1993</v>
@@ -2277,7 +2351,7 @@
         <v>1996</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -2285,7 +2359,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C8" s="9">
         <v>1996</v>
@@ -2294,7 +2368,7 @@
         <v>1999</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -2302,7 +2376,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C9" s="9">
         <v>1999</v>
@@ -2311,7 +2385,7 @@
         <v>2002</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -2319,7 +2393,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C10" s="9">
         <v>2002</v>
@@ -2336,7 +2410,7 @@
         <v>10</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C11" s="9">
         <v>2005</v>
@@ -2345,7 +2419,7 @@
         <v>2006</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -2353,7 +2427,7 @@
         <v>11</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C12" s="9">
         <v>2006</v>
@@ -2370,7 +2444,7 @@
         <v>12</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C13" s="9">
         <v>2018</v>
@@ -2387,7 +2461,7 @@
         <v>13</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C14" s="9">
         <v>2022</v>
@@ -2404,7 +2478,7 @@
         <v>14</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C15" s="9">
         <v>2024</v>
@@ -2427,7 +2501,7 @@
         <v>2026</v>
       </c>
       <c r="D16" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E16" t="s">
         <v>34</v>

--- a/excels/faculty.xlsx
+++ b/excels/faculty.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\NIT\Documents\PA_Catts\Nitw_WB\excels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D404DBB9-C461-44A0-89D3-74E03914ECA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B61F6C8B-971C-49BF-A559-7177D0052173}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CoreFaculty" sheetId="1" r:id="rId1"/>
@@ -20,6 +20,7 @@
     <sheet name="PreviousHOD" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="162913"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -32,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="170">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="173">
   <si>
     <t>Name</t>
   </si>
@@ -543,6 +544,15 @@
   </si>
   <si>
     <t>images/Guest Faculty/Carmelo D'agostino.jpg</t>
+  </si>
+  <si>
+    <t>View Profile</t>
+  </si>
+  <si>
+    <t>https://portal.research.lu.se/en/persons/aliaksei-laureshyn/</t>
+  </si>
+  <si>
+    <t>https://portal.research.lu.se/en/persons/carmelo-dagostino/</t>
   </si>
 </sst>
 </file>
@@ -1573,7 +1583,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:H11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.140625" customWidth="1"/>
@@ -1581,9 +1591,10 @@
     <col min="5" max="5" width="37.85546875" customWidth="1"/>
     <col min="6" max="6" width="29.42578125" customWidth="1"/>
     <col min="7" max="7" width="22.7109375" customWidth="1"/>
+    <col min="8" max="8" width="45.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1605,8 +1616,11 @@
       <c r="G1" s="3" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H1" s="3" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>162</v>
       </c>
@@ -1628,8 +1642,11 @@
       <c r="G2" t="s">
         <v>168</v>
       </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H2" s="2" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>159</v>
       </c>
@@ -1651,8 +1668,11 @@
       <c r="G3" t="s">
         <v>169</v>
       </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H3" s="2" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="4"/>
       <c r="B4" s="4"/>
       <c r="C4" s="4"/>
@@ -1661,7 +1681,7 @@
       <c r="F4" s="4"/>
       <c r="G4" s="4"/>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="4"/>
       <c r="B5" s="4"/>
       <c r="C5" s="4"/>
@@ -1670,7 +1690,7 @@
       <c r="F5" s="4"/>
       <c r="G5" s="4"/>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="4"/>
       <c r="B6" s="4"/>
       <c r="C6" s="4"/>
@@ -1679,7 +1699,7 @@
       <c r="F6" s="4"/>
       <c r="G6" s="4"/>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="4"/>
       <c r="B7" s="4"/>
       <c r="C7" s="4"/>
@@ -1688,7 +1708,7 @@
       <c r="F7" s="4"/>
       <c r="G7" s="4"/>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="4"/>
       <c r="B8" s="4"/>
       <c r="C8" s="4"/>
@@ -1697,7 +1717,7 @@
       <c r="F8" s="4"/>
       <c r="G8" s="4"/>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="4"/>
       <c r="B9" s="4"/>
       <c r="C9" s="4"/>
@@ -1706,7 +1726,7 @@
       <c r="F9" s="4"/>
       <c r="G9" s="4"/>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="4"/>
       <c r="B10" s="4"/>
       <c r="C10" s="4"/>
@@ -1715,7 +1735,7 @@
       <c r="F10" s="4"/>
       <c r="G10" s="4"/>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="4"/>
       <c r="B11" s="4"/>
       <c r="C11" s="4"/>
@@ -1728,6 +1748,8 @@
   <hyperlinks>
     <hyperlink ref="E3" r:id="rId1" display="https://portal.research.lu.se/en/persons/carmelo-dagostino/" xr:uid="{BB1D5C0B-7EE0-405C-981B-7A52C90A3CA8}"/>
     <hyperlink ref="E2" r:id="rId2" display="mailto:aliaksei.laureshyn@tft.lth.se" xr:uid="{427A828D-746B-478A-9530-7EDB1E3A7067}"/>
+    <hyperlink ref="H2" r:id="rId3" xr:uid="{572AF0AD-0528-4C33-9A76-3431BA8B9B27}"/>
+    <hyperlink ref="H3" r:id="rId4" xr:uid="{73BFF9D2-3B65-4653-904C-07FB5C2E52DB}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
